--- a/data/trans_dic/P3A$yo-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P3A$yo-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que la persona entrevistada se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente la persona entrevistada se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>40,56; 58,29</t>
+          <t>40,37; 57,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>60,14; 74,79</t>
+          <t>59,96; 74,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50,85; 63,34</t>
+          <t>51,59; 63,15</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>61,15; 73,23</t>
+          <t>61,95; 73,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>90,47; 96,4</t>
+          <t>90,53; 96,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>78,18; 86,26</t>
+          <t>77,94; 86,15</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>73,22; 80,57</t>
+          <t>73,35; 80,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>95,91; 98,22</t>
+          <t>96,15; 98,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>85,69; 90,32</t>
+          <t>85,6; 90,09</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>24,24; 74,38</t>
+          <t>22,16; 73,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>96,38; 98,26</t>
+          <t>96,21; 98,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43,43; 86,39</t>
+          <t>47,49; 86,38</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>64,96; 72,34</t>
+          <t>65,47; 72,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>95,6; 97,9</t>
+          <t>95,65; 97,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80,43; 84,56</t>
+          <t>80,45; 84,58</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>58,87; 67,4</t>
+          <t>58,75; 67,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>94,24; 98,71</t>
+          <t>94,11; 98,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>78,71; 92,1</t>
+          <t>78,75; 91,96</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>44,88; 54,18</t>
+          <t>44,51; 53,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>71,82; 77,74</t>
+          <t>71,55; 77,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>61,78; 67,37</t>
+          <t>61,85; 67,35</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>47,57; 66,49</t>
+          <t>46,73; 66,57</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>90,35; 93,16</t>
+          <t>90,37; 93,12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>67,01; 80,34</t>
+          <t>68,12; 80,32</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que la persona entrevistada se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente la persona entrevistada se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>162232; 233158</t>
+          <t>161492; 231365</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>188349; 234227</t>
+          <t>187793; 234205</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>362663; 451754</t>
+          <t>367899; 450402</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>259018; 310160</t>
+          <t>262396; 310726</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>463313; 493641</t>
+          <t>463617; 492918</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>731473; 807095</t>
+          <t>729196; 806067</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>392716; 432150</t>
+          <t>393380; 433318</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>567782; 581482</t>
+          <t>569197; 582220</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>966901; 1019170</t>
+          <t>965844; 1016498</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>215171; 660351</t>
+          <t>196737; 656396</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>686407; 699811</t>
+          <t>685192; 699957</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>694878; 1382222</t>
+          <t>759757; 1382062</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>364566; 406015</t>
+          <t>367447; 408419</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>523792; 536390</t>
+          <t>524057; 536275</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>892029; 937893</t>
+          <t>892336; 938071</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>216102; 247397</t>
+          <t>215662; 245997</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>572771; 599948</t>
+          <t>572028; 599535</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>767329; 897840</t>
+          <t>767722; 896448</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>126895; 153194</t>
+          <t>125844; 151896</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>305815; 331037</t>
+          <t>304700; 331225</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>437752; 477353</t>
+          <t>438262; 477248</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1645467; 2299797</t>
+          <t>1616269; 2302431</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3352739; 3457073</t>
+          <t>3353826; 3455773</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4804174; 5760368</t>
+          <t>4883769; 5758566</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A$yo-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P3A$yo-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>58,0%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>40,37; 57,84</t>
+          <t>40,36; 56,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>59,96; 74,78</t>
+          <t>60,71; 74,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51,59; 63,15</t>
+          <t>52,71; 64,1</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>79,6%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>61,95; 73,36</t>
+          <t>59,55; 71,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>90,53; 96,26</t>
+          <t>89,19; 95,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>77,94; 86,15</t>
+          <t>75,92; 82,52</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>86,26%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>73,35; 80,79</t>
+          <t>71,36; 79,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>96,15; 98,35</t>
+          <t>95,71; 98,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>85,6; 90,09</t>
+          <t>84,18; 88,13</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>85,16%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>22,16; 73,94</t>
+          <t>68,78; 75,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>96,21; 98,28</t>
+          <t>96,2; 98,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47,49; 86,38</t>
+          <t>83,3; 86,91</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>82,83%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>65,47; 72,77</t>
+          <t>65,4; 72,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>95,65; 97,88</t>
+          <t>95,71; 97,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80,45; 84,58</t>
+          <t>80,76; 84,64</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>79,02%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>58,75; 67,02</t>
+          <t>58,11; 66,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>94,11; 98,64</t>
+          <t>92,39; 95,78</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>78,75; 91,96</t>
+          <t>76,52; 81,14</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>64,49%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>44,51; 53,72</t>
+          <t>44,35; 53,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>71,55; 77,78</t>
+          <t>71,9; 77,96</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>61,85; 67,35</t>
+          <t>61,52; 67,07</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>78,41%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>46,73; 66,57</t>
+          <t>63,75; 67,23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>90,37; 93,12</t>
+          <t>89,56; 91,58</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>68,12; 80,32</t>
+          <t>77,31; 79,47</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>196451</t>
+          <t>199296</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>211927</t>
+          <t>247501</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>408377</t>
+          <t>446798</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>161492; 231365</t>
+          <t>164597; 230305</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>187793; 234205</t>
+          <t>220076; 270228</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>367899; 450402</t>
+          <t>406066; 493800</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>285935</t>
+          <t>313266</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>479432</t>
+          <t>465725</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>765367</t>
+          <t>778991</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>262396; 310726</t>
+          <t>283993; 339440</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>463617; 492918</t>
+          <t>447471; 477102</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>729196; 806067</t>
+          <t>743018; 807527</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>413336</t>
+          <t>468248</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>576164</t>
+          <t>604805</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>989500</t>
+          <t>1073052</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>393380; 433318</t>
+          <t>443059; 490534</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>569197; 582220</t>
+          <t>596453; 610883</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>965844; 1016498</t>
+          <t>1047200; 1096373</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>468927</t>
+          <t>507007</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>693913</t>
+          <t>716572</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1162839</t>
+          <t>1223579</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>196737; 656396</t>
+          <t>481908; 531551</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>685192; 699957</t>
+          <t>708240; 722718</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>759757; 1382062</t>
+          <t>1196863; 1248688</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>386377</t>
+          <t>418530</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>531277</t>
+          <t>590445</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>917654</t>
+          <t>1008976</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>367447; 408419</t>
+          <t>398525; 441204</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>524057; 536275</t>
+          <t>582729; 596311</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>892336; 938071</t>
+          <t>983837; 1031072</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>230492</t>
+          <t>253943</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>586226</t>
+          <t>413444</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>816720</t>
+          <t>667387</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>215662; 245997</t>
+          <t>235926; 270386</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>572028; 599535</t>
+          <t>405232; 420071</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>767722; 896448</t>
+          <t>646259; 685323</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>139089</t>
+          <t>152265</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>318639</t>
+          <t>347432</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>457728</t>
+          <t>499697</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>125844; 151896</t>
+          <t>137584; 166606</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>304700; 331225</t>
+          <t>334065; 362194</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>438262; 477248</t>
+          <t>476679; 519632</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2120608</t>
+          <t>2312557</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3397577</t>
+          <t>3385923</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5518185</t>
+          <t>5698481</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1616269; 2302431</t>
+          <t>2251481; 2374350</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3353826; 3455773</t>
+          <t>3345644; 3421280</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4883769; 5758566</t>
+          <t>5618246; 5775071</t>
         </is>
       </c>
     </row>
